--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-28 01:18</t>
+    <t xml:space="preserve">2026-08-17 16:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 16:06</t>
+    <t xml:space="preserve">2026-08-17 22:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 22:38</t>
+    <t xml:space="preserve">2026-09-06 21:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
